--- a/template.xlsx
+++ b/template.xlsx
@@ -1,15 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Siddharth S Bhandari\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_09380A55B3A535A53139DDD4C74E93A2F9B96B00" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12525"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="First Method" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -145,14 +162,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="29">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -212,159 +223,8 @@
       <name val="Trebuchet MS"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="39">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -385,7 +245,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -397,7 +257,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -407,194 +267,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="26">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -803,257 +477,63 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="22" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1063,18 +543,66 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1093,146 +621,18 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
-    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
-    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
-    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
-    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
-    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
-    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
-    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
-    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
-    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
-    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
-    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
-    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
-    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
-    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
-    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
-    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
-    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
-    <cellStyle name="Total" xfId="25" builtinId="25"/>
-    <cellStyle name="Output" xfId="26" builtinId="21"/>
-    <cellStyle name="Currency" xfId="27" builtinId="4"/>
-    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
-    <cellStyle name="Note" xfId="29" builtinId="10"/>
-    <cellStyle name="Input" xfId="30" builtinId="20"/>
-    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
-    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
-    <cellStyle name="Good" xfId="33" builtinId="26"/>
-    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
-    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
-    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
-    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
-    <cellStyle name="Title" xfId="39" builtinId="15"/>
-    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
-    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
-    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
-    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
-    <cellStyle name="Comma" xfId="44" builtinId="3"/>
-    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
-    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
-    <cellStyle name="Percent" xfId="47" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1519,841 +919,839 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="6.14" style="1" customWidth="1"/>
-    <col min="2" max="3" width="9.14" style="1"/>
-    <col min="4" max="4" width="9.14" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.2866666666667" style="1" customWidth="1"/>
-    <col min="6" max="11" width="10.7133333333333" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.14" style="1"/>
+    <col min="1" max="1" width="6.109375" style="1" customWidth="1"/>
+    <col min="2" max="3" width="9.109375" style="1"/>
+    <col min="4" max="4" width="9.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" style="1" customWidth="1"/>
+    <col min="6" max="11" width="10.6640625" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:11">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:11" ht="16.2">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-    </row>
-    <row r="2" ht="16.5" spans="1:11">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+    </row>
+    <row r="2" spans="1:11" ht="16.2">
+      <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="32"/>
-    </row>
-    <row r="3" ht="20.1" customHeight="1" spans="1:11">
-      <c r="A3" s="5" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="21"/>
+    </row>
+    <row r="3" spans="1:11" ht="20.100000000000001" customHeight="1">
+      <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="6">
+      <c r="B3" s="22"/>
+      <c r="C3" s="3">
         <v>70</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="2">
         <v>3</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="33">
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="23">
         <v>0.5</v>
       </c>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-    </row>
-    <row r="4" ht="20.1" customHeight="1" spans="1:11">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="6">
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+    </row>
+    <row r="4" spans="1:11" ht="20.100000000000001" customHeight="1">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="3">
         <v>60</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="4">
         <v>2</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="23"/>
-      <c r="I4" s="35" t="s">
+      <c r="H4" s="26"/>
+      <c r="I4" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="22" t="s">
+      <c r="J4" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="K4" s="23"/>
-    </row>
-    <row r="5" ht="27.75" customHeight="1" spans="1:11">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="6">
+      <c r="K4" s="26"/>
+    </row>
+    <row r="5" spans="1:11" ht="27.75" customHeight="1">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="3">
         <v>50</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="2">
         <v>1</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="24" t="s">
+      <c r="G5" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="25"/>
-      <c r="I5" s="36" t="s">
+      <c r="H5" s="28"/>
+      <c r="I5" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="37" t="s">
+      <c r="J5" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="38"/>
-    </row>
-    <row r="6" ht="20.1" customHeight="1" spans="1:11">
-      <c r="A6" s="8" t="s">
+      <c r="K5" s="30"/>
+    </row>
+    <row r="6" spans="1:11" ht="20.100000000000001" customHeight="1">
+      <c r="A6" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-    </row>
-    <row r="7" ht="20.1" customHeight="1" spans="1:11">
-      <c r="A7" s="9" t="s">
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+    </row>
+    <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1">
+      <c r="A7" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="26" t="s">
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8" t="s">
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" ht="30.75" customHeight="1" spans="1:11">
-      <c r="A8" s="12"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="8" t="s">
+    <row r="8" spans="1:11" ht="30.75" customHeight="1">
+      <c r="A8" s="44"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="K8" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" ht="20.1" customHeight="1" spans="1:11">
-      <c r="A9" s="15" t="s">
+    <row r="9" spans="1:11" ht="20.100000000000001" customHeight="1">
+      <c r="A9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="8">
+      <c r="D9" s="32"/>
+      <c r="E9" s="5">
         <v>15</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="5">
         <v>4.5</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="5">
         <v>4.5</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="5">
         <v>6</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="5">
         <v>100</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="5">
         <v>100</v>
       </c>
-      <c r="K9" s="8">
+      <c r="K9" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="10" ht="20.1" customHeight="1" spans="1:11">
-      <c r="A10" s="15">
+    <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1">
+      <c r="A10" s="6">
         <v>1</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15">
+      <c r="D10" s="32"/>
+      <c r="E10" s="6">
         <v>15</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="11">
         <f>E10*$F$9/$E$9</f>
         <v>4.5</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="11">
         <f>E10*$G$9/$E$9</f>
         <v>4.5</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="11">
         <f>E10*$H$9/$E$9</f>
         <v>6</v>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="11">
         <f>(F10*100)/$F$9</f>
         <v>100</v>
       </c>
-      <c r="J10" s="28">
+      <c r="J10" s="11">
         <f>(G10*100)/$G$9</f>
         <v>100</v>
       </c>
-      <c r="K10" s="28">
+      <c r="K10" s="11">
         <f>(H10*100)/$H$9</f>
         <v>100</v>
       </c>
     </row>
-    <row r="11" ht="20.1" customHeight="1" spans="1:11">
-      <c r="A11" s="15">
+    <row r="11" spans="1:11" ht="20.100000000000001" customHeight="1">
+      <c r="A11" s="6">
         <v>2</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15">
+      <c r="D11" s="32"/>
+      <c r="E11" s="6">
         <v>15</v>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="11">
         <v>3</v>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="11">
         <v>4</v>
       </c>
-      <c r="H11" s="28">
+      <c r="H11" s="11">
         <f t="shared" ref="H11:H20" si="0">E11*$H$9/$E$9</f>
         <v>6</v>
       </c>
-      <c r="I11" s="28">
+      <c r="I11" s="11">
         <f t="shared" ref="I11:I20" si="1">(F11*100)/$F$9</f>
-        <v>66.6666666666667</v>
-      </c>
-      <c r="J11" s="28">
+        <v>66.666666666666671</v>
+      </c>
+      <c r="J11" s="11">
         <f t="shared" ref="J11:J20" si="2">(G11*100)/$G$9</f>
-        <v>88.8888888888889</v>
-      </c>
-      <c r="K11" s="28">
+        <v>88.888888888888886</v>
+      </c>
+      <c r="K11" s="11">
         <f t="shared" ref="K11:K20" si="3">(H11*100)/$H$9</f>
         <v>100</v>
       </c>
     </row>
-    <row r="12" ht="20.1" customHeight="1" spans="1:11">
-      <c r="A12" s="15">
+    <row r="12" spans="1:11" ht="20.100000000000001" customHeight="1">
+      <c r="A12" s="6">
         <v>3</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15">
+      <c r="D12" s="32"/>
+      <c r="E12" s="6">
         <v>12</v>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="11">
         <f t="shared" ref="F12:F20" si="4">E12*$F$9/$E$9</f>
         <v>3.6</v>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="11">
         <f t="shared" ref="G12:G20" si="5">E12*$G$9/$E$9</f>
         <v>3.6</v>
       </c>
-      <c r="H12" s="28">
+      <c r="H12" s="11">
         <f t="shared" si="0"/>
         <v>4.8</v>
       </c>
-      <c r="I12" s="28">
+      <c r="I12" s="11">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="J12" s="28">
+      <c r="J12" s="11">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="K12" s="28">
+      <c r="K12" s="11">
         <f t="shared" si="3"/>
         <v>80</v>
       </c>
     </row>
-    <row r="13" ht="20.1" customHeight="1" spans="1:11">
-      <c r="A13" s="15">
+    <row r="13" spans="1:11" ht="20.100000000000001" customHeight="1">
+      <c r="A13" s="6">
         <v>4</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15">
+      <c r="D13" s="32"/>
+      <c r="E13" s="6">
         <v>15</v>
       </c>
-      <c r="F13" s="28">
+      <c r="F13" s="11">
         <f t="shared" si="4"/>
         <v>4.5</v>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="11">
         <f t="shared" si="5"/>
         <v>4.5</v>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I13" s="28">
+      <c r="I13" s="11">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="J13" s="28">
+      <c r="J13" s="11">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="K13" s="28">
+      <c r="K13" s="11">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
     </row>
-    <row r="14" ht="20.1" customHeight="1" spans="1:11">
-      <c r="A14" s="15">
+    <row r="14" spans="1:11" ht="20.100000000000001" customHeight="1">
+      <c r="A14" s="6">
         <v>5</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15">
+      <c r="D14" s="32"/>
+      <c r="E14" s="6">
         <v>5</v>
       </c>
-      <c r="F14" s="28">
+      <c r="F14" s="11">
         <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="11">
         <f t="shared" si="5"/>
         <v>1.5</v>
       </c>
-      <c r="H14" s="28">
+      <c r="H14" s="11">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="I14" s="28">
+      <c r="I14" s="11">
         <f t="shared" si="1"/>
-        <v>33.3333333333333</v>
-      </c>
-      <c r="J14" s="28">
+        <v>33.333333333333336</v>
+      </c>
+      <c r="J14" s="11">
         <f t="shared" si="2"/>
-        <v>33.3333333333333</v>
-      </c>
-      <c r="K14" s="28">
+        <v>33.333333333333336</v>
+      </c>
+      <c r="K14" s="11">
         <f t="shared" si="3"/>
-        <v>33.3333333333333</v>
-      </c>
-    </row>
-    <row r="15" ht="20.1" customHeight="1" spans="1:11">
-      <c r="A15" s="15">
+        <v>33.333333333333336</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="20.100000000000001" customHeight="1">
+      <c r="A15" s="6">
         <v>6</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15">
+      <c r="D15" s="32"/>
+      <c r="E15" s="6">
         <v>12</v>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="11">
         <f t="shared" si="4"/>
         <v>3.6</v>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="11">
         <f t="shared" si="5"/>
         <v>3.6</v>
       </c>
-      <c r="H15" s="28">
+      <c r="H15" s="11">
         <f t="shared" si="0"/>
         <v>4.8</v>
       </c>
-      <c r="I15" s="28">
+      <c r="I15" s="11">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="J15" s="28">
+      <c r="J15" s="11">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="K15" s="28">
+      <c r="K15" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="20.1" customHeight="1" spans="1:11">
-      <c r="A16" s="15">
+    <row r="16" spans="1:11" ht="20.100000000000001" customHeight="1">
+      <c r="A16" s="6">
         <v>7</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15">
+      <c r="D16" s="32"/>
+      <c r="E16" s="6">
         <v>2</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="11">
         <f t="shared" si="4"/>
         <v>0.6</v>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="11">
         <f t="shared" si="5"/>
         <v>0.6</v>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="11">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="I16" s="28">
+      <c r="I16" s="11">
         <f t="shared" si="1"/>
-        <v>13.3333333333333</v>
-      </c>
-      <c r="J16" s="28">
+        <v>13.333333333333334</v>
+      </c>
+      <c r="J16" s="11">
         <f t="shared" si="2"/>
-        <v>13.3333333333333</v>
-      </c>
-      <c r="K16" s="28">
+        <v>13.333333333333334</v>
+      </c>
+      <c r="K16" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="17" ht="20.1" customHeight="1" spans="1:11">
-      <c r="A17" s="15">
+    <row r="17" spans="1:11" ht="20.100000000000001" customHeight="1">
+      <c r="A17" s="6">
         <v>8</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15">
+      <c r="D17" s="32"/>
+      <c r="E17" s="6">
         <v>10</v>
       </c>
-      <c r="F17" s="28">
+      <c r="F17" s="11">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="G17" s="28">
+      <c r="G17" s="11">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="H17" s="28">
+      <c r="H17" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I17" s="28">
+      <c r="I17" s="11">
         <f t="shared" si="1"/>
-        <v>66.6666666666667</v>
-      </c>
-      <c r="J17" s="28">
+        <v>66.666666666666671</v>
+      </c>
+      <c r="J17" s="11">
         <f t="shared" si="2"/>
-        <v>66.6666666666667</v>
-      </c>
-      <c r="K17" s="28">
+        <v>66.666666666666671</v>
+      </c>
+      <c r="K17" s="11">
         <f t="shared" si="3"/>
-        <v>66.6666666666667</v>
-      </c>
-    </row>
-    <row r="18" ht="20.1" customHeight="1" spans="1:11">
-      <c r="A18" s="15">
+        <v>66.666666666666671</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="20.100000000000001" customHeight="1">
+      <c r="A18" s="6">
         <v>9</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15">
+      <c r="D18" s="32"/>
+      <c r="E18" s="6">
         <v>12</v>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="11">
         <f t="shared" si="4"/>
         <v>3.6</v>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="11">
         <f t="shared" si="5"/>
         <v>3.6</v>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="11">
         <f t="shared" si="0"/>
         <v>4.8</v>
       </c>
-      <c r="I18" s="28">
+      <c r="I18" s="11">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="J18" s="28">
+      <c r="J18" s="11">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="K18" s="28">
+      <c r="K18" s="11">
         <f t="shared" si="3"/>
         <v>80</v>
       </c>
     </row>
-    <row r="19" ht="20.1" customHeight="1" spans="1:11">
-      <c r="A19" s="15">
+    <row r="19" spans="1:11" ht="20.100000000000001" customHeight="1">
+      <c r="A19" s="6">
         <v>10</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15">
+      <c r="D19" s="32"/>
+      <c r="E19" s="6">
         <v>6</v>
       </c>
-      <c r="F19" s="28">
+      <c r="F19" s="11">
         <f t="shared" si="4"/>
         <v>1.8</v>
       </c>
-      <c r="G19" s="28">
+      <c r="G19" s="11">
         <f t="shared" si="5"/>
         <v>1.8</v>
       </c>
-      <c r="H19" s="28">
+      <c r="H19" s="11">
         <f t="shared" si="0"/>
         <v>2.4</v>
       </c>
-      <c r="I19" s="28">
+      <c r="I19" s="11">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="J19" s="28">
+      <c r="J19" s="11">
         <f t="shared" si="2"/>
         <v>40</v>
       </c>
-      <c r="K19" s="28">
+      <c r="K19" s="11">
         <f t="shared" si="3"/>
         <v>40</v>
       </c>
     </row>
-    <row r="20" ht="20.1" customHeight="1" spans="1:11">
-      <c r="A20" s="16">
+    <row r="20" spans="1:11" ht="20.100000000000001" customHeight="1">
+      <c r="A20" s="7">
         <v>11</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15">
+      <c r="D20" s="32"/>
+      <c r="E20" s="6">
         <v>11</v>
       </c>
-      <c r="F20" s="28">
+      <c r="F20" s="11">
         <f t="shared" si="4"/>
         <v>3.3</v>
       </c>
-      <c r="G20" s="28">
+      <c r="G20" s="11">
         <f t="shared" si="5"/>
         <v>3.3</v>
       </c>
-      <c r="H20" s="28">
+      <c r="H20" s="11">
         <f t="shared" si="0"/>
-        <v>4.4</v>
-      </c>
-      <c r="I20" s="28">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="I20" s="11">
         <f t="shared" si="1"/>
-        <v>73.3333333333333</v>
-      </c>
-      <c r="J20" s="28">
+        <v>73.333333333333329</v>
+      </c>
+      <c r="J20" s="11">
         <f t="shared" si="2"/>
-        <v>73.3333333333333</v>
-      </c>
-      <c r="K20" s="28">
+        <v>73.333333333333329</v>
+      </c>
+      <c r="K20" s="11">
         <f t="shared" si="3"/>
-        <v>73.3333333333333</v>
-      </c>
-    </row>
-    <row r="21" ht="24.95" customHeight="1" spans="1:11">
-      <c r="A21" s="17" t="s">
+        <v>73.333333333333343</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="24.9" customHeight="1">
+      <c r="A21" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="18">
+      <c r="B21" s="33"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="9">
         <f>(I25+J25+K25)/3</f>
-        <v>2.66666666666667</v>
-      </c>
-      <c r="E21" s="18"/>
-      <c r="F21" s="29" t="s">
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="E21" s="9"/>
+      <c r="F21" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="G21" s="30" t="s">
+      <c r="G21" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="H21" s="30"/>
-      <c r="I21" s="39">
+      <c r="H21" s="34"/>
+      <c r="I21" s="14">
         <f>COUNTIF(I10:I20,"AB")</f>
         <v>0</v>
       </c>
-      <c r="J21" s="39">
+      <c r="J21" s="14">
         <f t="shared" ref="J21:K21" si="6">COUNTIF(J10:J20,"AB")</f>
         <v>0</v>
       </c>
-      <c r="K21" s="39">
+      <c r="K21" s="14">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" ht="24.95" customHeight="1" spans="1:11">
-      <c r="A22" s="17" t="s">
+    <row r="22" spans="1:11" ht="24.9" customHeight="1">
+      <c r="A22" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17" t="s">
+      <c r="B22" s="33"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="17"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="31" t="s">
+      <c r="E22" s="8"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="H22" s="31"/>
-      <c r="I22" s="40">
+      <c r="H22" s="35"/>
+      <c r="I22" s="15">
         <v>11</v>
       </c>
-      <c r="J22" s="40">
+      <c r="J22" s="15">
         <v>11</v>
       </c>
-      <c r="K22" s="40">
+      <c r="K22" s="15">
         <v>11</v>
       </c>
     </row>
-    <row r="23" ht="24.95" customHeight="1" spans="1:11">
-      <c r="A23" s="19" t="s">
+    <row r="23" spans="1:11" ht="24.9" customHeight="1">
+      <c r="A23" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="18" t="s">
+      <c r="B23" s="36"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="18"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="31" t="s">
+      <c r="E23" s="9"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="H23" s="31"/>
-      <c r="I23" s="40">
+      <c r="H23" s="35"/>
+      <c r="I23" s="15">
         <f>COUNTIF(I10:I20,"&gt;50")</f>
         <v>8</v>
       </c>
-      <c r="J23" s="40">
+      <c r="J23" s="15">
         <f t="shared" ref="J23:K23" si="7">COUNTIF(J10:J20,"&gt;50")</f>
         <v>8</v>
       </c>
-      <c r="K23" s="40">
+      <c r="K23" s="15">
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
     </row>
-    <row r="24" ht="24.95" customHeight="1" spans="1:11">
-      <c r="A24" s="19" t="s">
+    <row r="24" spans="1:11" ht="24.9" customHeight="1">
+      <c r="A24" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="18" t="s">
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="18"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="31" t="s">
+      <c r="E24" s="9"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="H24" s="31"/>
-      <c r="I24" s="41">
+      <c r="H24" s="35"/>
+      <c r="I24" s="16">
         <f t="shared" ref="I24:K24" si="8">(I23*100)/11</f>
-        <v>72.7272727272727</v>
-      </c>
-      <c r="J24" s="41">
+        <v>72.727272727272734</v>
+      </c>
+      <c r="J24" s="16">
         <f t="shared" si="8"/>
-        <v>72.7272727272727</v>
-      </c>
-      <c r="K24" s="41">
+        <v>72.727272727272734</v>
+      </c>
+      <c r="K24" s="16">
         <f t="shared" si="8"/>
-        <v>63.6363636363636</v>
-      </c>
-    </row>
-    <row r="25" ht="39.75" customHeight="1" spans="1:11">
-      <c r="A25" s="20" t="s">
+        <v>63.636363636363633</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="39.75" customHeight="1">
+      <c r="A25" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="18" t="s">
+      <c r="B25" s="37"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E25" s="18"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="31" t="s">
+      <c r="E25" s="9"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="H25" s="31"/>
-      <c r="I25" s="42">
+      <c r="H25" s="35"/>
+      <c r="I25" s="17">
         <f t="shared" ref="I25:K25" si="9">IF(I24&gt;70,3,IF(I24&gt;60,2,IF(I24&gt;50,1,0)))</f>
         <v>3</v>
       </c>
-      <c r="J25" s="42">
+      <c r="J25" s="17">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="K25" s="42">
+      <c r="K25" s="17">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
     </row>
-    <row r="26" ht="15.75"/>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C3:C5" name="Range1"/>
   </protectedRanges>
   <mergeCells count="36">
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="F21:F25"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="A7:D8"/>
+    <mergeCell ref="A3:B5"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="J4:K4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="A6:K6"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F21:F25"/>
-    <mergeCell ref="A7:D8"/>
-    <mergeCell ref="A3:B5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="80" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/template.xlsx
+++ b/template.xlsx
@@ -1,32 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Siddharth S Bhandari\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_09380A55B3A535A53139DDD4C74E93A2F9B96B00" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12525"/>
   </bookViews>
   <sheets>
     <sheet name="First Method" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -162,8 +145,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,8 +212,159 @@
       <name val="Trebuchet MS"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -245,7 +385,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -257,7 +397,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -267,8 +407,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -477,162 +803,436 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="22" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
+    <cellStyle name="Total" xfId="25" builtinId="25"/>
+    <cellStyle name="Output" xfId="26" builtinId="21"/>
+    <cellStyle name="Currency" xfId="27" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
+    <cellStyle name="Note" xfId="29" builtinId="10"/>
+    <cellStyle name="Input" xfId="30" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
+    <cellStyle name="Good" xfId="33" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
+    <cellStyle name="Comma" xfId="44" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
+    <cellStyle name="Percent" xfId="47" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -919,839 +1519,841 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K25"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.109375" style="1" customWidth="1"/>
-    <col min="2" max="3" width="9.109375" style="1"/>
-    <col min="4" max="4" width="9.109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" style="1" customWidth="1"/>
-    <col min="6" max="11" width="10.6640625" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="6.14" style="1" customWidth="1"/>
+    <col min="2" max="3" width="9.14" style="1"/>
+    <col min="4" max="4" width="9.14" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.2866666666667" style="1" customWidth="1"/>
+    <col min="6" max="11" width="10.7133333333333" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.14" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="16.2">
-      <c r="A1" s="18" t="s">
+    <row r="1" ht="16.5" spans="1:11">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-    </row>
-    <row r="2" spans="1:11" ht="16.2">
-      <c r="A2" s="19" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+    </row>
+    <row r="2" ht="16.5" spans="1:11">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="21"/>
-    </row>
-    <row r="3" spans="1:11" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="22" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="32"/>
+    </row>
+    <row r="3" ht="20.1" customHeight="1" spans="1:11">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="3">
+      <c r="B3" s="5"/>
+      <c r="C3" s="6">
         <v>70</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="5">
         <v>3</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="23">
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="33">
         <v>0.5</v>
       </c>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-    </row>
-    <row r="4" spans="1:11" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="3">
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+    </row>
+    <row r="4" ht="20.1" customHeight="1" spans="1:11">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="6">
         <v>60</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="7">
         <v>2</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="25" t="s">
+      <c r="G4" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="26"/>
-      <c r="I4" s="12" t="s">
+      <c r="H4" s="23"/>
+      <c r="I4" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="25" t="s">
+      <c r="J4" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="K4" s="26"/>
-    </row>
-    <row r="5" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A5" s="22"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="3">
+      <c r="K4" s="23"/>
+    </row>
+    <row r="5" ht="27.75" customHeight="1" spans="1:11">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="6">
         <v>50</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="5">
         <v>1</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="28"/>
-      <c r="I5" s="13" t="s">
+      <c r="H5" s="25"/>
+      <c r="I5" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="29" t="s">
+      <c r="J5" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="30"/>
-    </row>
-    <row r="6" spans="1:11" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="31" t="s">
+      <c r="K5" s="38"/>
+    </row>
+    <row r="6" ht="20.1" customHeight="1" spans="1:11">
+      <c r="A6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-    </row>
-    <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="41" t="s">
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+    </row>
+    <row r="7" ht="20.1" customHeight="1" spans="1:11">
+      <c r="A7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="38" t="s">
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="31" t="s">
+      <c r="F7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="5" t="s">
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="30.75" customHeight="1">
-      <c r="A8" s="44"/>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="5" t="s">
+    <row r="8" ht="30.75" customHeight="1" spans="1:11">
+      <c r="A8" s="12"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="6" t="s">
+    <row r="9" ht="20.1" customHeight="1" spans="1:11">
+      <c r="A9" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="32"/>
-      <c r="E9" s="5">
+      <c r="D9" s="15"/>
+      <c r="E9" s="8">
         <v>15</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="8">
         <v>4.5</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="8">
         <v>4.5</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="8">
         <v>6</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="8">
         <v>100</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="8">
         <v>100</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9" s="8">
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="6">
+    <row r="10" ht="20.1" customHeight="1" spans="1:11">
+      <c r="A10" s="15">
         <v>1</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="6">
+      <c r="D10" s="15"/>
+      <c r="E10" s="15">
         <v>15</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="28">
         <f>E10*$F$9/$E$9</f>
         <v>4.5</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="28">
         <f>E10*$G$9/$E$9</f>
         <v>4.5</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="28">
         <f>E10*$H$9/$E$9</f>
         <v>6</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="28">
         <f>(F10*100)/$F$9</f>
         <v>100</v>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="28">
         <f>(G10*100)/$G$9</f>
         <v>100</v>
       </c>
-      <c r="K10" s="11">
+      <c r="K10" s="28">
         <f>(H10*100)/$H$9</f>
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="6">
+    <row r="11" ht="20.1" customHeight="1" spans="1:11">
+      <c r="A11" s="15">
         <v>2</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="32"/>
-      <c r="E11" s="6">
+      <c r="D11" s="15"/>
+      <c r="E11" s="15">
         <v>15</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="28">
         <v>3</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="28">
         <v>4</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="28">
         <f t="shared" ref="H11:H20" si="0">E11*$H$9/$E$9</f>
         <v>6</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="28">
         <f t="shared" ref="I11:I20" si="1">(F11*100)/$F$9</f>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="J11" s="11">
+        <v>66.6666666666667</v>
+      </c>
+      <c r="J11" s="28">
         <f t="shared" ref="J11:J20" si="2">(G11*100)/$G$9</f>
-        <v>88.888888888888886</v>
-      </c>
-      <c r="K11" s="11">
+        <v>88.8888888888889</v>
+      </c>
+      <c r="K11" s="28">
         <f t="shared" ref="K11:K20" si="3">(H11*100)/$H$9</f>
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="6">
+    <row r="12" ht="20.1" customHeight="1" spans="1:11">
+      <c r="A12" s="15">
         <v>3</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="32"/>
-      <c r="E12" s="6">
+      <c r="D12" s="15"/>
+      <c r="E12" s="15">
         <v>12</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="28">
         <f t="shared" ref="F12:F20" si="4">E12*$F$9/$E$9</f>
         <v>3.6</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="28">
         <f t="shared" ref="G12:G20" si="5">E12*$G$9/$E$9</f>
         <v>3.6</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="28">
         <f t="shared" si="0"/>
         <v>4.8</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="28">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="J12" s="11">
+      <c r="J12" s="28">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="K12" s="11">
+      <c r="K12" s="28">
         <f t="shared" si="3"/>
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="6">
+    <row r="13" ht="20.1" customHeight="1" spans="1:11">
+      <c r="A13" s="15">
         <v>4</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="32"/>
-      <c r="E13" s="6">
+      <c r="D13" s="15"/>
+      <c r="E13" s="15">
         <v>15</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="28">
         <f t="shared" si="4"/>
         <v>4.5</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="28">
         <f t="shared" si="5"/>
         <v>4.5</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="28">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="28">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="J13" s="11">
+      <c r="J13" s="28">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="K13" s="11">
+      <c r="K13" s="28">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="6">
+    <row r="14" ht="20.1" customHeight="1" spans="1:11">
+      <c r="A14" s="15">
         <v>5</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="32"/>
-      <c r="E14" s="6">
+      <c r="D14" s="15"/>
+      <c r="E14" s="15">
         <v>5</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="28">
         <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="28">
         <f t="shared" si="5"/>
         <v>1.5</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="28">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="28">
         <f t="shared" si="1"/>
-        <v>33.333333333333336</v>
-      </c>
-      <c r="J14" s="11">
+        <v>33.3333333333333</v>
+      </c>
+      <c r="J14" s="28">
         <f t="shared" si="2"/>
-        <v>33.333333333333336</v>
-      </c>
-      <c r="K14" s="11">
+        <v>33.3333333333333</v>
+      </c>
+      <c r="K14" s="28">
         <f t="shared" si="3"/>
-        <v>33.333333333333336</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="6">
+        <v>33.3333333333333</v>
+      </c>
+    </row>
+    <row r="15" ht="20.1" customHeight="1" spans="1:11">
+      <c r="A15" s="15">
         <v>6</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="32" t="s">
+      <c r="C15" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="32"/>
-      <c r="E15" s="6">
+      <c r="D15" s="15"/>
+      <c r="E15" s="15">
         <v>12</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="28">
         <f t="shared" si="4"/>
         <v>3.6</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="28">
         <f t="shared" si="5"/>
         <v>3.6</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="28">
         <f t="shared" si="0"/>
         <v>4.8</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="28">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="J15" s="11">
+      <c r="J15" s="28">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="K15" s="11">
+      <c r="K15" s="28">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="6">
+    <row r="16" ht="20.1" customHeight="1" spans="1:11">
+      <c r="A16" s="15">
         <v>7</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="6">
+      <c r="D16" s="15"/>
+      <c r="E16" s="15">
         <v>2</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="28">
         <f t="shared" si="4"/>
         <v>0.6</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="28">
         <f t="shared" si="5"/>
         <v>0.6</v>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="28">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="28">
         <f t="shared" si="1"/>
-        <v>13.333333333333334</v>
-      </c>
-      <c r="J16" s="11">
+        <v>13.3333333333333</v>
+      </c>
+      <c r="J16" s="28">
         <f t="shared" si="2"/>
-        <v>13.333333333333334</v>
-      </c>
-      <c r="K16" s="11">
+        <v>13.3333333333333</v>
+      </c>
+      <c r="K16" s="28">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="6">
+    <row r="17" ht="20.1" customHeight="1" spans="1:11">
+      <c r="A17" s="15">
         <v>8</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C17" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="32"/>
-      <c r="E17" s="6">
+      <c r="D17" s="15"/>
+      <c r="E17" s="15">
         <v>10</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="28">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I17" s="11">
+      <c r="I17" s="28">
         <f t="shared" si="1"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="J17" s="11">
+        <v>66.6666666666667</v>
+      </c>
+      <c r="J17" s="28">
         <f t="shared" si="2"/>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="K17" s="11">
+        <v>66.6666666666667</v>
+      </c>
+      <c r="K17" s="28">
         <f t="shared" si="3"/>
-        <v>66.666666666666671</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="6">
+        <v>66.6666666666667</v>
+      </c>
+    </row>
+    <row r="18" ht="20.1" customHeight="1" spans="1:11">
+      <c r="A18" s="15">
         <v>9</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="32" t="s">
+      <c r="C18" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="32"/>
-      <c r="E18" s="6">
+      <c r="D18" s="15"/>
+      <c r="E18" s="15">
         <v>12</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="28">
         <f t="shared" si="4"/>
         <v>3.6</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="28">
         <f t="shared" si="5"/>
         <v>3.6</v>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="28">
         <f t="shared" si="0"/>
         <v>4.8</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="28">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="J18" s="11">
+      <c r="J18" s="28">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="K18" s="11">
+      <c r="K18" s="28">
         <f t="shared" si="3"/>
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="6">
+    <row r="19" ht="20.1" customHeight="1" spans="1:11">
+      <c r="A19" s="15">
         <v>10</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="32" t="s">
+      <c r="C19" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="32"/>
-      <c r="E19" s="6">
+      <c r="D19" s="15"/>
+      <c r="E19" s="15">
         <v>6</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="28">
         <f t="shared" si="4"/>
         <v>1.8</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="28">
         <f t="shared" si="5"/>
         <v>1.8</v>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="28">
         <f t="shared" si="0"/>
         <v>2.4</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="28">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="J19" s="11">
+      <c r="J19" s="28">
         <f t="shared" si="2"/>
         <v>40</v>
       </c>
-      <c r="K19" s="11">
+      <c r="K19" s="28">
         <f t="shared" si="3"/>
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="7">
+    <row r="20" ht="20.1" customHeight="1" spans="1:11">
+      <c r="A20" s="16">
         <v>11</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="32"/>
-      <c r="E20" s="6">
+      <c r="D20" s="15"/>
+      <c r="E20" s="15">
         <v>11</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F20" s="28">
         <f t="shared" si="4"/>
         <v>3.3</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="28">
         <f t="shared" si="5"/>
         <v>3.3</v>
       </c>
-      <c r="H20" s="11">
+      <c r="H20" s="28">
         <f t="shared" si="0"/>
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="I20" s="11">
+        <v>4.4</v>
+      </c>
+      <c r="I20" s="28">
         <f t="shared" si="1"/>
-        <v>73.333333333333329</v>
-      </c>
-      <c r="J20" s="11">
+        <v>73.3333333333333</v>
+      </c>
+      <c r="J20" s="28">
         <f t="shared" si="2"/>
-        <v>73.333333333333329</v>
-      </c>
-      <c r="K20" s="11">
+        <v>73.3333333333333</v>
+      </c>
+      <c r="K20" s="28">
         <f t="shared" si="3"/>
-        <v>73.333333333333343</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="24.9" customHeight="1">
-      <c r="A21" s="33" t="s">
+        <v>73.3333333333333</v>
+      </c>
+    </row>
+    <row r="21" ht="24.95" customHeight="1" spans="1:11">
+      <c r="A21" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="33"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="9">
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="18">
         <f>(I25+J25+K25)/3</f>
-        <v>2.6666666666666665</v>
-      </c>
-      <c r="E21" s="9"/>
-      <c r="F21" s="40" t="s">
+        <v>2.66666666666667</v>
+      </c>
+      <c r="E21" s="18"/>
+      <c r="F21" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="G21" s="34" t="s">
+      <c r="G21" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="H21" s="34"/>
-      <c r="I21" s="14">
+      <c r="H21" s="30"/>
+      <c r="I21" s="39">
         <f>COUNTIF(I10:I20,"AB")</f>
         <v>0</v>
       </c>
-      <c r="J21" s="14">
+      <c r="J21" s="39">
         <f t="shared" ref="J21:K21" si="6">COUNTIF(J10:J20,"AB")</f>
         <v>0</v>
       </c>
-      <c r="K21" s="14">
+      <c r="K21" s="39">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="24.9" customHeight="1">
-      <c r="A22" s="33" t="s">
+    <row r="22" ht="24.95" customHeight="1" spans="1:11">
+      <c r="A22" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="33"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="8" t="s">
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="8"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="35" t="s">
+      <c r="E22" s="17"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="H22" s="35"/>
-      <c r="I22" s="15">
+      <c r="H22" s="31"/>
+      <c r="I22" s="40">
         <v>11</v>
       </c>
-      <c r="J22" s="15">
+      <c r="J22" s="40">
         <v>11</v>
       </c>
-      <c r="K22" s="15">
+      <c r="K22" s="40">
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="24.9" customHeight="1">
-      <c r="A23" s="36" t="s">
+    <row r="23" ht="24.95" customHeight="1" spans="1:11">
+      <c r="A23" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="9" t="s">
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="9"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="35" t="s">
+      <c r="E23" s="18"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="H23" s="35"/>
-      <c r="I23" s="15">
+      <c r="H23" s="31"/>
+      <c r="I23" s="40">
         <f>COUNTIF(I10:I20,"&gt;50")</f>
         <v>8</v>
       </c>
-      <c r="J23" s="15">
+      <c r="J23" s="40">
         <f t="shared" ref="J23:K23" si="7">COUNTIF(J10:J20,"&gt;50")</f>
         <v>8</v>
       </c>
-      <c r="K23" s="15">
+      <c r="K23" s="40">
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="24.9" customHeight="1">
-      <c r="A24" s="36" t="s">
+    <row r="24" ht="24.95" customHeight="1" spans="1:11">
+      <c r="A24" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="36"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="9" t="s">
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="9"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="35" t="s">
+      <c r="E24" s="18"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="H24" s="35"/>
-      <c r="I24" s="16">
+      <c r="H24" s="31"/>
+      <c r="I24" s="41">
         <f t="shared" ref="I24:K24" si="8">(I23*100)/11</f>
-        <v>72.727272727272734</v>
-      </c>
-      <c r="J24" s="16">
+        <v>72.7272727272727</v>
+      </c>
+      <c r="J24" s="41">
         <f t="shared" si="8"/>
-        <v>72.727272727272734</v>
-      </c>
-      <c r="K24" s="16">
+        <v>72.7272727272727</v>
+      </c>
+      <c r="K24" s="41">
         <f t="shared" si="8"/>
-        <v>63.636363636363633</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="39.75" customHeight="1">
-      <c r="A25" s="37" t="s">
+        <v>63.6363636363636</v>
+      </c>
+    </row>
+    <row r="25" ht="39.75" customHeight="1" spans="1:11">
+      <c r="A25" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="37"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="9" t="s">
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="E25" s="9"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="35" t="s">
+      <c r="E25" s="18"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="H25" s="35"/>
-      <c r="I25" s="17">
+      <c r="H25" s="31"/>
+      <c r="I25" s="42">
         <f t="shared" ref="I25:K25" si="9">IF(I24&gt;70,3,IF(I24&gt;60,2,IF(I24&gt;50,1,0)))</f>
         <v>3</v>
       </c>
-      <c r="J25" s="17">
+      <c r="J25" s="42">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="K25" s="17">
+      <c r="K25" s="42">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
     </row>
+    <row r="26" ht="15.75"/>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C3:C5" name="Range1"/>
   </protectedRanges>
   <mergeCells count="36">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="G22:H22"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="G23:H23"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="G25:H25"/>
+    <mergeCell ref="E7:E8"/>
     <mergeCell ref="F21:F25"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="A6:K6"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E7:E8"/>
     <mergeCell ref="A7:D8"/>
     <mergeCell ref="A3:B5"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="J4:K4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="80" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
